--- a/Inventory_BITM_vtiger/src/test/resources/vtiger_testdata.xlsx
+++ b/Inventory_BITM_vtiger/src/test/resources/vtiger_testdata.xlsx
@@ -5,21 +5,20 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\eclipse-workspace\Inventory_BITM_vtiger\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\git\vtigerSprint\Inventory_BITM_vtiger\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EE21662-61E5-4904-8A27-3E075CA46A5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85EE5626-6A7C-4BD5-9620-8EAA35030EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="6" xr2:uid="{6658EF05-967A-4259-A01F-90B3AF662524}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="4" xr2:uid="{6658EF05-967A-4259-A01F-90B3AF662524}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
-    <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
-    <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
-    <sheet name="Sheet7" sheetId="7" r:id="rId7"/>
+    <sheet name="Sheet6" sheetId="6" r:id="rId5"/>
+    <sheet name="Sheet7" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="41">
   <si>
     <t>Service Name</t>
   </si>
@@ -54,9 +53,6 @@
     <t>Website Development</t>
   </si>
   <si>
-    <t>Software Testing</t>
-  </si>
-  <si>
     <t>Data Entry</t>
   </si>
   <si>
@@ -129,15 +125,6 @@
     <t>Updated installation and configuration support</t>
   </si>
   <si>
-    <t>OriginalServiceName</t>
-  </si>
-  <si>
-    <t>UpdatedServiceName</t>
-  </si>
-  <si>
-    <t>Software Testing Updated</t>
-  </si>
-  <si>
     <t>SN1001</t>
   </si>
   <si>
@@ -172,6 +159,9 @@
   </si>
   <si>
     <t>pasword</t>
+  </si>
+  <si>
+    <t>Software Quality Assurance</t>
   </si>
 </sst>
 </file>
@@ -181,7 +171,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-14009]yyyy/mm/dd;@"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -196,6 +186,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -218,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -245,6 +240,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -560,7 +556,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF6BC2C9-6BDA-43D1-8BBC-0CE7FF6AB293}">
   <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="25.81640625" customWidth="1"/>
     <col min="2" max="2" width="12.6328125" customWidth="1"/>
@@ -570,7 +566,7 @@
     <col min="6" max="6" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -581,10 +577,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" s="3" customFormat="1">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -595,12 +591,12 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="3" customFormat="1" ht="29">
+      <c r="A3" s="10" t="s">
+        <v>40</v>
       </c>
       <c r="B3" s="2">
         <v>15000</v>
@@ -609,12 +605,12 @@
         <v>5</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" s="3" customFormat="1">
       <c r="A4" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" s="2">
         <v>500</v>
@@ -623,76 +619,76 @@
         <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" s="3" customFormat="1">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" s="3" customFormat="1">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" s="3" customFormat="1">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" s="3" customFormat="1">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" s="3" customFormat="1">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" s="3" customFormat="1">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" s="3" customFormat="1">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" s="3" customFormat="1">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" s="3" customFormat="1">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" s="3" customFormat="1">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
     </row>
-    <row r="15" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" s="3" customFormat="1">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
     </row>
-    <row r="16" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" s="3" customFormat="1">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -707,25 +703,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D439ACE-7022-42A0-BD84-88189575226B}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="29">
       <c r="A1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:4" ht="29">
       <c r="A2" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" s="6">
         <v>1</v>
@@ -737,13 +733,13 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -757,7 +753,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3B8522A-2DDC-4DA8-8640-612E95B4F85B}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="18.7265625" style="3" customWidth="1"/>
     <col min="2" max="2" width="10.453125" style="3" customWidth="1"/>
@@ -769,50 +765,50 @@
     <col min="8" max="16384" width="8.7265625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="29">
       <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:8" ht="43.5">
       <c r="A2" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" s="7">
         <v>46342</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="G2" s="2">
         <v>1</v>
@@ -830,33 +826,33 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7472D1A0-ABC6-43FC-BEE0-616CD86D9F96}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="18.36328125" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="39.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" t="s">
-        <v>27</v>
-      </c>
       <c r="C1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -865,39 +861,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBF78EC6-754E-404F-8DEF-9E2C2EB2E254}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="21.453125" customWidth="1"/>
-    <col min="2" max="2" width="26.6328125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12D2851A-3EC3-4F07-817F-090CB0BF98BE}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="14.08984375" customWidth="1"/>
     <col min="2" max="2" width="11.54296875" customWidth="1"/>
@@ -905,29 +871,29 @@
     <col min="4" max="4" width="14.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" s="8" customFormat="1">
       <c r="A1" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:4" s="3" customFormat="1">
       <c r="A2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="D2" s="9">
         <v>46312</v>
@@ -939,39 +905,39 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE3A8B77-EC31-4DCA-8D06-2CD780319EA7}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="10.453125" customWidth="1"/>
     <col min="2" max="2" width="11.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2">
       <c r="A1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="B3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
